--- a/株式会社鶴岡中央青果/追加資料依頼リスト_鶴岡中央青果_260923.xlsx
+++ b/株式会社鶴岡中央青果/追加資料依頼リスト_鶴岡中央青果_260923.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ご確認事項" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'資料依頼リスト'!$A$5:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'資料依頼リスト'!$A$5:$I$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'資料依頼リスト'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -503,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1643,22 +1643,22 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>人事</t>
+          <t>財務</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>社会保険・労働保険の加入状況、36協定</t>
+          <t>売掛金年齢表・残高証明書（評価基準日時点）</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>未払残業代の有無を含む</t>
+          <t>2026年3月末の得意先別売掛金の発生月別残高、預金残高証明書</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>労務リスクの確認</t>
+          <t>株式価値評価（修正BS）で売掛金・現預金を評価するため（現在は簿価評価）</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -1676,22 +1676,22 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>事業</t>
+          <t>人事</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>設備投資・修繕の予定</t>
+          <t>賃金規程（賞与の支給対象期間を含む）</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>冷蔵設備・車両・建物改修の今後の予定額</t>
+          <t>賞与の算定期間・支給月の定め</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>買収後の投資負担の見積り</t>
+          <t>賞与引当金の計上要否と正常収益力の算定（評価書）</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -1703,31 +1703,97 @@
       <c r="H39" s="5" t="inlineStr"/>
       <c r="I39" s="5" t="inlineStr"/>
     </row>
-    <row r="41">
-      <c r="B41" s="9" t="inlineStr">
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>人事</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>社会保険・労働保険の加入状況、36協定</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>未払残業代の有無を含む</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>労務リスクの確認</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>事業</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>設備投資・修繕の予定</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>冷蔵設備・車両・建物改修の今後の予定額</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>買収後の投資負担の見積り</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>受領済み資料（2026年9月時点）</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>・決算報告書 第51期（2024/3）〜第53期（2026/3）（勘定科目内訳明細書・法人税申告書・法人事業概況説明書を含む）</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="2" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>・試算表（2026年7月分）　・履歴事項全部証明書（2026/9/10）　・職員名簿（2026/9/1現在）　・R8年度 固定資産税課税明細書</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:I39"/>
+  <autoFilter ref="A5:I41"/>
   <dataValidations count="1">
-    <dataValidation sqref="F6:F39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F6:F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
   </dataValidations>
